--- a/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>176 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-3.72778</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-73.25066</v>
-      </c>
-      <c r="I2" t="n">
-        <v>320</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-3.72778</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-73.25066</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>329 MI MUNDO FELIZ</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-3.72261</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-73.25718999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>234</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-3.72261</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-73.25719</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>344 MI PRIMER APRENDIZAJE</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-3.72744</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-73.25605</v>
-      </c>
-      <c r="I4" t="n">
-        <v>254</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-3.72744</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-73.25605</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>704 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-3.72515</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-73.24611</v>
-      </c>
-      <c r="I5" t="n">
-        <v>220</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-3.72515</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-73.24611</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>705</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-3.72537</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-73.24517</v>
-      </c>
-      <c r="I6" t="n">
-        <v>265</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-3.72537</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-73.24517</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>707 PASITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-3.71982</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-73.24003</v>
-      </c>
-      <c r="I7" t="n">
-        <v>137</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-3.71982</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-73.24003</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>60052 GENERALISIMO JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-3.72551</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-73.24981</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2051</v>
-      </c>
-      <c r="J8" t="n">
-        <v>102</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-3.72551</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-73.24981</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>60057 PETRONILA PEREDA DE FERRANDO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-3.713664</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-73.24542099999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1215</v>
-      </c>
-      <c r="J9" t="n">
-        <v>58</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-3.713664</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-73.245421</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>60063</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-3.711448</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-73.240408</v>
-      </c>
-      <c r="I10" t="n">
-        <v>710</v>
-      </c>
-      <c r="J10" t="n">
-        <v>34</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-3.711448</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-73.240408</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>60115 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-3.698347</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-73.278469</v>
-      </c>
-      <c r="I11" t="n">
-        <v>687</v>
-      </c>
-      <c r="J11" t="n">
-        <v>36</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-3.698347</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-73.278469</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>61015 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-3.730463</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-73.24382300000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1179</v>
-      </c>
-      <c r="J12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-3.730463</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-73.243823</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>601452</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-3.7135</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-73.23905000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>367</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-3.7135</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-73.23905</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>601457 LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-3.72137</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.25758</v>
-      </c>
-      <c r="I14" t="n">
-        <v>277</v>
-      </c>
-      <c r="J14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-3.72137</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-73.25758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>601458</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-3.719517</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-73.24014200000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>251</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-3.719517</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-73.240142</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>601486 ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-3.7245</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.2625</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1197</v>
-      </c>
-      <c r="J16" t="n">
-        <v>52</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-3.7245</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.2625</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1197</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>6010120</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-3.7254</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-73.24476</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1019</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.7254</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-73.24476</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>NUESTRA SEÑORA DE LA SALUD</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-3.72752</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-73.25391</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1266</v>
-      </c>
-      <c r="J18" t="n">
-        <v>69</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.72752</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-73.25391</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>813 GOTITAS DE AMOR</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-3.71237</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-73.23899</v>
-      </c>
-      <c r="I19" t="n">
-        <v>229</v>
-      </c>
-      <c r="J19" t="n">
-        <v>9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-3.71237</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.23899</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>60974 MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-3.72604</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-73.25066</v>
-      </c>
-      <c r="I20" t="n">
-        <v>344</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-3.72604</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-73.25066</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>373066</t>
+          <t>373373</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>176 SEÑOR DE LOS MILAGROS</t>
+          <t>60052 GENERALISIMO JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.72778</t>
+          <t>-3.72551</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.25066</t>
+          <t>-73.24981</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>373349</t>
+          <t>373066</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>707 PASITOS DE JESUS</t>
+          <t>176 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.71982</t>
+          <t>-3.72778</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.24003</t>
+          <t>-73.25066</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>373373</t>
+          <t>373863</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60052 GENERALISIMO JOSE DE SAN MARTIN</t>
+          <t>601457 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.72551</t>
+          <t>-3.72137</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.24981</t>
+          <t>-73.25758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>373387</t>
+          <t>373877</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60057 PETRONILA PEREDA DE FERRANDO</t>
+          <t>601458</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.713664</t>
+          <t>-3.719517</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.245421</t>
+          <t>-73.240142</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>373429</t>
+          <t>814244</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>60974 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.711448</t>
+          <t>-3.72604</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.240408</t>
+          <t>-73.25066</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>373504</t>
+          <t>373844</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60115 MIGUEL GRAU SEMINARIO</t>
+          <t>601452</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.698347</t>
+          <t>-3.7135</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.278469</t>
+          <t>-73.23905</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>373759</t>
+          <t>373429</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61015 LA INMACULADA</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.730463</t>
+          <t>-3.711448</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.243823</t>
+          <t>-73.240408</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>710</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>373844</t>
+          <t>373504</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>601452</t>
+          <t>60115 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.7135</t>
+          <t>-3.698347</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.23905</t>
+          <t>-73.278469</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>687</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>373863</t>
+          <t>373882</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>601457 LEONCIO PRADO</t>
+          <t>601486 ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.72137</t>
+          <t>-3.7245</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.25758</t>
+          <t>-73.2625</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>373877</t>
+          <t>373957</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>601458</t>
+          <t>6010120</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.719517</t>
+          <t>-3.7254</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.240142</t>
+          <t>-73.24476</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>373882</t>
+          <t>373759</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>601486 ALEXANDER VON HUMBOLDT</t>
+          <t>61015 LA INMACULADA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.7245</t>
+          <t>-3.730463</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.2625</t>
+          <t>-73.243823</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>373957</t>
+          <t>373387</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6010120</t>
+          <t>60057 PETRONILA PEREDA DE FERRANDO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.7254</t>
+          <t>-3.713664</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.24476</t>
+          <t>-73.245421</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>374117</t>
+          <t>373349</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SALUD</t>
+          <t>707 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.72752</t>
+          <t>-3.71982</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.25391</t>
+          <t>-73.24003</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>740823</t>
+          <t>374117</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>813 GOTITAS DE AMOR</t>
+          <t>NUESTRA SEÑORA DE LA SALUD</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.71237</t>
+          <t>-3.72752</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.23899</t>
+          <t>-73.25391</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>814244</t>
+          <t>740823</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60974 MARIANO MELGAR</t>
+          <t>813 GOTITAS DE AMOR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.72604</t>
+          <t>-3.71237</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.25066</t>
+          <t>-73.23899</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>373373</t>
+          <t>814244</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60052 GENERALISIMO JOSE DE SAN MARTIN</t>
+          <t>60974 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.72551</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.24981</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>-3.72604</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>-73.25066</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>373085</t>
+          <t>740823</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>329 MI MUNDO FELIZ</t>
+          <t>813 GOTITAS DE AMOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.72261</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.25719</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-3.71237</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.23899</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>373113</t>
+          <t>374117</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>344 MI PRIMER APRENDIZAJE</t>
+          <t>NUESTRA SEÑORA DE LA SALUD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.72744</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.25605</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-3.72752</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.25391</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>373325</t>
+          <t>373957</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>704 VIRGEN DE FATIMA</t>
+          <t>6010120</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.72515</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.24611</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-3.7254</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.24476</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>373330</t>
+          <t>373882</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>601486 ALEXANDER VON HUMBOLDT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.72537</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.24517</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-3.7245</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.2625</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>373066</t>
+          <t>373877</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>176 SEÑOR DE LOS MILAGROS</t>
+          <t>601458</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.72778</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.25066</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>-3.719517</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-73.240142</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>-3.72137</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>-73.25758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>373877</t>
+          <t>373844</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>601458</t>
+          <t>601452</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.719517</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.240142</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-3.7135</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.23905</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>814244</t>
+          <t>373759</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60974 MARIANO MELGAR</t>
+          <t>61015 LA INMACULADA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.72604</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.25066</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-3.730463</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.243823</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>373844</t>
+          <t>373504</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>601452</t>
+          <t>60115 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.7135</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.23905</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-3.698347</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-73.278469</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-3.711448</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-73.240408</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>373504</t>
+          <t>373387</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60115 MIGUEL GRAU SEMINARIO</t>
+          <t>60057 PETRONILA PEREDA DE FERRANDO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.698347</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.278469</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>-3.713664</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-73.245421</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>373882</t>
+          <t>373373</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>601486 ALEXANDER VON HUMBOLDT</t>
+          <t>60052 GENERALISIMO JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.7245</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.2625</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>-3.72551</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-73.24981</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>373957</t>
+          <t>373349</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6010120</t>
+          <t>707 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.7254</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.24476</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>-3.71982</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-73.24003</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>373759</t>
+          <t>373330</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61015 LA INMACULADA</t>
+          <t>705</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.730463</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.243823</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>-3.72537</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-73.24517</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>373387</t>
+          <t>373325</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60057 PETRONILA PEREDA DE FERRANDO</t>
+          <t>704 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.713664</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.245421</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>-3.72515</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-73.24611</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>373349</t>
+          <t>373113</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>707 PASITOS DE JESUS</t>
+          <t>344 MI PRIMER APRENDIZAJE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.71982</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.24003</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>-3.72744</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-73.25605</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>374117</t>
+          <t>373085</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SALUD</t>
+          <t>329 MI MUNDO FELIZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.72752</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.25391</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>-3.72261</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-73.25719</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>740823</t>
+          <t>373066</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>813 GOTITAS DE AMOR</t>
+          <t>176 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.71237</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.23899</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-3.72778</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-73.25066</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-PUNCHANA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
